--- a/benchmarks/dementia_special_issue/cross_cohort/dementia_full_cross_cohort_source_data.xlsx
+++ b/benchmarks/dementia_special_issue/cross_cohort/dementia_full_cross_cohort_source_data.xlsx
@@ -4131,12 +4131,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>overlap_cpgs</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>jaccard</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>overlap_cpgs</t>
         </is>
       </c>
     </row>
@@ -4165,13 +4165,13 @@
       <c r="F2" t="n">
         <v>4</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>cg00709979;cg04315214;cg14622549;cg20240347</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
         <v>0.001571091908876669</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>cg00709979;cg04315214;cg14622549;cg20240347</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -4199,10 +4199,10 @@
       <c r="F3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4229,10 +4229,10 @@
       <c r="F4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4259,10 +4259,10 @@
       <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4289,10 +4289,10 @@
       <c r="F6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4319,10 +4319,10 @@
       <c r="F7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4349,13 +4349,13 @@
       <c r="F8" t="n">
         <v>6</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>cg05066959;cg05810363;cg07584855;cg12309456;cg17104258;cg18102633</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
         <v>0.02068965517241379</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>cg05066959;cg05810363;cg07584855;cg12309456;cg17104258;cg18102633</t>
-        </is>
       </c>
     </row>
     <row r="9">
@@ -4383,10 +4383,10 @@
       <c r="F9" t="n">
         <v>0</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4413,10 +4413,10 @@
       <c r="F10" t="n">
         <v>0</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4443,10 +4443,10 @@
       <c r="F11" t="n">
         <v>0</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4473,10 +4473,10 @@
       <c r="F12" t="n">
         <v>0</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4503,10 +4503,10 @@
       <c r="F13" t="n">
         <v>0</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4533,10 +4533,10 @@
       <c r="F14" t="n">
         <v>0</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4563,10 +4563,10 @@
       <c r="F15" t="n">
         <v>0</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4593,10 +4593,10 @@
       <c r="F16" t="n">
         <v>0</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4623,13 +4623,13 @@
       <c r="F17" t="n">
         <v>4</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>cg00709979;cg04315214;cg14622549;cg20240347</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
         <v>0.001190476190476191</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>cg00709979;cg04315214;cg14622549;cg20240347</t>
-        </is>
       </c>
     </row>
     <row r="18">
@@ -4657,10 +4657,10 @@
       <c r="F18" t="n">
         <v>0</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4687,10 +4687,10 @@
       <c r="F19" t="n">
         <v>0</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4717,10 +4717,10 @@
       <c r="F20" t="n">
         <v>0</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4747,10 +4747,10 @@
       <c r="F21" t="n">
         <v>0</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4777,10 +4777,10 @@
       <c r="F22" t="n">
         <v>0</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4807,13 +4807,13 @@
       <c r="F23" t="n">
         <v>6</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>cg05066959;cg05810363;cg07584855;cg12309456;cg17104258;cg18102633</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
         <v>0.01863354037267081</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>cg05066959;cg05810363;cg07584855;cg12309456;cg17104258;cg18102633</t>
-        </is>
       </c>
     </row>
     <row r="24">
@@ -4841,10 +4841,10 @@
       <c r="F24" t="n">
         <v>0</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4871,10 +4871,10 @@
       <c r="F25" t="n">
         <v>0</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4901,10 +4901,10 @@
       <c r="F26" t="n">
         <v>0</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4931,10 +4931,10 @@
       <c r="F27" t="n">
         <v>0</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4961,10 +4961,10 @@
       <c r="F28" t="n">
         <v>0</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4991,10 +4991,10 @@
       <c r="F29" t="n">
         <v>0</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5021,10 +5021,10 @@
       <c r="F30" t="n">
         <v>0</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5051,10 +5051,10 @@
       <c r="F31" t="n">
         <v>0</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
